--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39D.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B66EF8-3154-4A68-8EB7-B39A40F24C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70B104-F92B-4ACA-8CDA-62F30746ECAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>49006</t>
   </si>
@@ -121,52 +121,31 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>281AD7B9CE75ABACA6122601C75194B9</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Transparencia/acta%20de%20segunda%20sesi%c3%b3n%202024.pdf</t>
+  </si>
+  <si>
     <t>Unidad de Transparencia</t>
   </si>
   <si>
+    <t>09/10/2024</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>BBA478D0B07A8ED24C69B395D6AF6DDF</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Transparencia/calendario%20de%20sesiones%20ordinarias%202024.pdf</t>
-  </si>
-  <si>
-    <t>04/07/2024</t>
-  </si>
-  <si>
-    <t>3E79E7BC5042C9E65CE8360DC5E9D801</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Transparencia/acta%20transparencia%202024.pdf</t>
-  </si>
-  <si>
-    <t>ECBDC7A19DC62CE098CBE1E230D133F8</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Transparencia/acta%20archivo%202024.pdf</t>
   </si>
 </sst>
 </file>
@@ -572,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
@@ -737,107 +716,37 @@
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
